--- a/data/processed/india_rice_com_inad.xlsx
+++ b/data/processed/india_rice_com_inad.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wfp-my.sharepoint.com/personal/gabriel_battcock_wfp_org/Documents/Documents/MIMI_mac/nsso_hces_2023/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{5AAC3027-D2E5-4F46-8735-9EF7B553F89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61F59905-F323-4B1D-8120-1125B50998D0}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{5AAC3027-D2E5-4F46-8735-9EF7B553F89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61419327-FBFA-4CB5-95CF-F358890EFDF0}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-570" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-570" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="india_rice_com_inad" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="81">
   <si>
     <t>category</t>
   </si>
@@ -258,6 +271,12 @@
   </si>
   <si>
     <t>Urban 5</t>
+  </si>
+  <si>
+    <t>fol_fort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vb12_fort </t>
   </si>
 </sst>
 </file>
@@ -804,9 +823,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -844,7 +863,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -950,7 +969,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1092,7 +1111,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1100,13 +1119,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA55"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:BC55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.54296875" customWidth="1"/>
+    <col min="1" max="2" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1263,8 +1282,14 @@
       <c r="BA1" t="s">
         <v>51</v>
       </c>
+      <c r="BB1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1424,8 +1449,16 @@
       <c r="BA2">
         <v>21.993879317609</v>
       </c>
+      <c r="BB2" t="str">
+        <f>ROUND(C2,0) &amp;"("&amp;ROUND((C2-S2)*100/C2,0)&amp;")"</f>
+        <v>44(21)</v>
+      </c>
+      <c r="BC2" t="str">
+        <f>ROUND(E2,0)&amp;"("&amp;ROUND((E2-U2)*100/E2,0)&amp;")"</f>
+        <v>46(10)</v>
+      </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1586,7 +1619,7 @@
         <v>17.077293318233298</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1747,7 +1780,7 @@
         <v>24.425697865353001</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1908,7 +1941,7 @@
         <v>43.030360531309299</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2069,7 +2102,7 @@
         <v>52.936111111111103</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2230,7 +2263,7 @@
         <v>19.354558610709098</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2391,7 +2424,7 @@
         <v>40.772209567198203</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2552,7 +2585,7 @@
         <v>43.0142194744977</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2713,7 +2746,7 @@
         <v>30.276003649635001</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2874,7 +2907,7 @@
         <v>27.075055406701701</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3035,7 +3068,7 @@
         <v>11.5472851073736</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3196,7 +3229,7 @@
         <v>16.197090567808502</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3357,7 +3390,7 @@
         <v>26.154936582939602</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3518,7 +3551,7 @@
         <v>22.923252032520299</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3679,7 +3712,7 @@
         <v>19.432780082987598</v>
       </c>
     </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3840,7 +3873,7 @@
         <v>15.3595661846496</v>
       </c>
     </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4001,7 +4034,7 @@
         <v>5.8679808841099197</v>
       </c>
     </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4162,7 +4195,7 @@
         <v>14.5344129554656</v>
       </c>
     </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4323,7 +4356,7 @@
         <v>17.060581204593401</v>
       </c>
     </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4484,7 +4517,7 @@
         <v>12.9274794414703</v>
       </c>
     </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4645,7 +4678,7 @@
         <v>17.382223618090499</v>
       </c>
     </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4806,7 +4839,7 @@
         <v>13.991862766659301</v>
       </c>
     </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4967,7 +5000,7 @@
         <v>15.446389056527901</v>
       </c>
     </row>
-    <row r="25" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5128,7 +5161,7 @@
         <v>27.340138457191301</v>
       </c>
     </row>
-    <row r="26" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5289,7 +5322,7 @@
         <v>30.407496225241999</v>
       </c>
     </row>
-    <row r="27" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5450,7 +5483,7 @@
         <v>27.324404761904798</v>
       </c>
     </row>
-    <row r="28" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5611,7 +5644,7 @@
         <v>32.105256201260097</v>
       </c>
     </row>
-    <row r="29" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5772,7 +5805,7 @@
         <v>14.464794264951401</v>
       </c>
     </row>
-    <row r="30" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5933,7 +5966,7 @@
         <v>16.1705615060045</v>
       </c>
     </row>
-    <row r="31" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6094,7 +6127,7 @@
         <v>7.67746686303387</v>
       </c>
     </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6255,7 +6288,7 @@
         <v>14.9835255354201</v>
       </c>
     </row>
-    <row r="33" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6416,7 +6449,7 @@
         <v>19.673097826087002</v>
       </c>
     </row>
-    <row r="34" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6577,7 +6610,7 @@
         <v>16.2260111576011</v>
       </c>
     </row>
-    <row r="35" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6738,7 +6771,7 @@
         <v>19.391181988743</v>
       </c>
     </row>
-    <row r="36" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6899,7 +6932,7 @@
         <v>18.7963709677419</v>
       </c>
     </row>
-    <row r="37" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -7060,7 +7093,7 @@
         <v>17.5898043864849</v>
       </c>
     </row>
-    <row r="38" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -7221,7 +7254,7 @@
         <v>13.499304589707901</v>
       </c>
     </row>
-    <row r="39" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -7382,7 +7415,7 @@
         <v>24.835469962632899</v>
       </c>
     </row>
-    <row r="40" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -7543,7 +7576,7 @@
         <v>21.744778719489499</v>
       </c>
     </row>
-    <row r="41" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7704,7 +7737,7 @@
         <v>20.795485387717701</v>
       </c>
     </row>
-    <row r="42" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7865,7 +7898,7 @@
         <v>20.047357973343399</v>
       </c>
     </row>
-    <row r="43" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8026,7 +8059,7 @@
         <v>22.566148229836099</v>
       </c>
     </row>
-    <row r="44" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8187,7 +8220,7 @@
         <v>20.489757673667199</v>
       </c>
     </row>
-    <row r="45" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8348,7 +8381,7 @@
         <v>24.182898845126601</v>
       </c>
     </row>
-    <row r="46" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8509,7 +8542,7 @@
         <v>24.856857546227701</v>
       </c>
     </row>
-    <row r="47" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8670,7 +8703,7 @@
         <v>21.844324766943799</v>
       </c>
     </row>
-    <row r="48" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8831,7 +8864,7 @@
         <v>19.9330644144712</v>
       </c>
     </row>
-    <row r="49" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8992,7 +9025,7 @@
         <v>18.659273211444201</v>
       </c>
     </row>
-    <row r="50" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -9153,7 +9186,7 @@
         <v>17.441779078646</v>
       </c>
     </row>
-    <row r="51" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -9314,7 +9347,7 @@
         <v>26.379824063564101</v>
       </c>
     </row>
-    <row r="52" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -9475,7 +9508,7 @@
         <v>23.816729038130902</v>
       </c>
     </row>
-    <row r="53" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -9636,7 +9669,7 @@
         <v>22.494663007014299</v>
       </c>
     </row>
-    <row r="54" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -9797,7 +9830,7 @@
         <v>21.9604226705091</v>
       </c>
     </row>
-    <row r="55" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -9966,12 +9999,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34D73418-311D-4824-86B7-5BCDF9ECB4E6}">
   <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -10045,7 +10078,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44.064970128721797</v>
       </c>
@@ -10119,7 +10152,7 @@
         <v>18.3322267455851</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>26.358561045555401</v>
       </c>
@@ -10193,7 +10226,7 @@
         <v>9.5134268147956398</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>16.6214118424868</v>
       </c>
@@ -10267,7 +10300,7 @@
         <v>17.665819844669699</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>23.843079981228598</v>
       </c>
@@ -10341,7 +10374,7 @@
         <v>55.033064559978101</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>30.480872526915402</v>
       </c>
@@ -10415,7 +10448,7 @@
         <v>68.221661971719101</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>17.754987870233599</v>
       </c>
@@ -10489,7 +10522,7 @@
         <v>12.285255040828901</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>30.0112843339747</v>
       </c>
@@ -10563,7 +10596,7 @@
         <v>50.456222547762799</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>29.365345635802399</v>
       </c>
@@ -10637,7 +10670,7 @@
         <v>53.024437047613098</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>33.693961889360303</v>
       </c>
@@ -10711,7 +10744,7 @@
         <v>35.7861899777362</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>42.685532381049697</v>
       </c>
@@ -10785,7 +10818,7 @@
         <v>21.927528856999899</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>34.799988749950103</v>
       </c>
@@ -10859,7 +10892,7 @@
         <v>4.54195261646987</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45.0550589339582</v>
       </c>
@@ -10933,7 +10966,7 @@
         <v>3.2028944052970201</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>67.3840569942911</v>
       </c>
@@ -11007,7 +11040,7 @@
         <v>18.2223725112685</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>73.922934528622605</v>
       </c>
@@ -11081,7 +11114,7 @@
         <v>12.9415811904711</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>83.744576074858202</v>
       </c>
@@ -11155,7 +11188,7 @@
         <v>11.0045983576917</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>81.309257037412294</v>
       </c>
@@ -11229,7 +11262,7 @@
         <v>5.4505917177652199</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>53.968168133078102</v>
       </c>
@@ -11303,7 +11336,7 @@
         <v>1.97114794628873</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>69.538808158880897</v>
       </c>
@@ -11377,7 +11410,7 @@
         <v>5.7500288312848902</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>76.983379101342805</v>
       </c>
@@ -11451,7 +11484,7 @@
         <v>7.74045875673501</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>58.488966977397403</v>
       </c>
@@ -11525,7 +11558,7 @@
         <v>4.5155590688286704</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>59.6759800136103</v>
       </c>
@@ -11599,7 +11632,7 @@
         <v>9.2490569037522601</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>58.482163643259398</v>
       </c>
@@ -11673,7 +11706,7 @@
         <v>6.5849920777480104</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>49.711070499625997</v>
       </c>
@@ -11747,7 +11780,7 @@
         <v>11.354235150653899</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>29.140975430050201</v>
       </c>
@@ -11821,7 +11854,7 @@
         <v>26.275407659663799</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>33.033360161181903</v>
       </c>
@@ -11895,7 +11928,7 @@
         <v>34.391487562213499</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>32.884559575033599</v>
       </c>
@@ -11969,7 +12002,7 @@
         <v>17.9269494946804</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>42.4791252523531</v>
       </c>
@@ -12043,7 +12076,7 @@
         <v>32.7220905040719</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>51.187239705045798</v>
       </c>
@@ -12117,7 +12150,7 @@
         <v>6.4572287038428904</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>31.358934375310898</v>
       </c>
@@ -12191,7 +12224,7 @@
         <v>9.7462611492982507</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>24.453405295120099</v>
       </c>
@@ -12265,7 +12298,7 @@
         <v>2.08982183640427</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>79.387088434965094</v>
       </c>
@@ -12339,7 +12372,7 @@
         <v>6.8051984677332502</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>64.717083701778293</v>
       </c>
@@ -12413,7 +12446,7 @@
         <v>9.50741900522174</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>44.388204081350999</v>
       </c>
@@ -12487,7 +12520,7 @@
         <v>8.8702218463311908</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>48.7789925066511</v>
       </c>
@@ -12561,7 +12594,7 @@
         <v>7.4232440768301098</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>61.515128103959</v>
       </c>
@@ -12635,7 +12668,7 @@
         <v>6.97960192085114</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>65.054848443502294</v>
       </c>
@@ -12709,7 +12742,7 @@
         <v>13.427892217745301</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>52.465585792421003</v>
       </c>
@@ -12783,7 +12816,7 @@
         <v>1.41884209847126</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>57.366973070661501</v>
       </c>
@@ -12857,7 +12890,7 @@
         <v>18.917989951833199</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>46.971635291181798</v>
       </c>
@@ -12931,7 +12964,7 @@
         <v>17.441676755810199</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>42.536224530109003</v>
       </c>
@@ -13005,7 +13038,7 @@
         <v>17.330944503490102</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>37.472415636129497</v>
       </c>
@@ -13079,7 +13112,7 @@
         <v>16.701998930885701</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>32.7592062893047</v>
       </c>
@@ -13153,7 +13186,7 @@
         <v>21.408967314601899</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>44.988900674569301</v>
       </c>
@@ -13227,7 +13260,7 @@
         <v>15.979049617696001</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>42.051087605480099</v>
       </c>
@@ -13301,7 +13334,7 @@
         <v>23.461424303336599</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>60.172619098472197</v>
       </c>
@@ -13375,7 +13408,7 @@
         <v>17.658518883602</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>48.673171664851999</v>
       </c>
@@ -13449,7 +13482,7 @@
         <v>16.7951581638963</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>43.248951470256202</v>
       </c>
@@ -13523,7 +13556,7 @@
         <v>15.3014929179679</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>39.183240757045603</v>
       </c>
@@ -13597,7 +13630,7 @@
         <v>14.6717772107051</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>32.726121169312201</v>
       </c>
@@ -13671,7 +13704,7 @@
         <v>15.347698052663899</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>55.918073002269097</v>
       </c>
@@ -13745,7 +13778,7 @@
         <v>27.4119798673571</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>48.17283412111</v>
       </c>
@@ -13819,7 +13852,7 @@
         <v>23.716213939087599</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>41.426088524152</v>
       </c>
@@ -13893,7 +13926,7 @@
         <v>20.823086081956198</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>34.370252772328598</v>
       </c>
@@ -13967,7 +14000,7 @@
         <v>19.550616421953801</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>33.3646181581219</v>
       </c>
